--- a/tame_output/ON/bt/strategyON_20240823.xlsx
+++ b/tame_output/ON/bt/strategyON_20240823.xlsx
@@ -49023,16 +49023,16 @@
         <v>4.190494507880807</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.044080156114133</v>
+        <v>-5.044067229324755</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.172506021121406</v>
+        <v>2.172511191837158</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7205779073426514</v>
+        <v>0.7205988338669589</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.622841252286398</v>
+        <v>4.622853808200983</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240823.xlsx
+++ b/tame_output/ON/bt/strategyON_20240823.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.6%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>431.0%</t>
+          <t>430.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-666.0%</t>
+          <t>-668.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.0%</t>
+          <t>-160.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.7%</t>
+          <t>-331.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-151.9%</t>
+          <t>-154.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.327715739928527</v>
+        <v>-4.351654121421943</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.099803718178974</v>
+        <v>2.090228365581607</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9275632619981236</v>
+        <v>0.9036248805047076</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.387784395663006</v>
+        <v>4.373421366766957</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.334338986618885</v>
+        <v>-4.358277368112301</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.099035049686966</v>
+        <v>2.0894596970896</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9209400153077651</v>
+        <v>0.8970016338143492</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.385691077832927</v>
+        <v>4.371328048936878</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.231458397090292</v>
+        <v>-4.255396778583708</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.153038311376286</v>
+        <v>2.14346295877892</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.023820604836358</v>
+        <v>0.9998822233429421</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.460270457427965</v>
+        <v>4.445907428531916</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.254900436270379</v>
+        <v>-4.278838817763795</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.163864165877845</v>
+        <v>2.154288813280479</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.023820604836358</v>
+        <v>0.9998822233429421</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.480473127601559</v>
+        <v>4.46611009870551</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.272972944561991</v>
+        <v>-4.296911326055406</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.156635162561201</v>
+        <v>2.147059809963834</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.023820604836358</v>
+        <v>0.9998822233429421</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.480473127601559</v>
+        <v>4.46611009870551</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.504146738438623</v>
+        <v>-4.528085119932038</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.024417558604015</v>
+        <v>2.014842206006648</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.023820604836358</v>
+        <v>0.9998822233429421</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.440725041195027</v>
+        <v>4.426362012298976</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.472860717898167</v>
+        <v>-4.496799099391583</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.043954585817137</v>
+        <v>2.034379233219771</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.055106625376813</v>
+        <v>1.031168243883398</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.466519272516239</v>
+        <v>4.452156243620189</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.319835325784883</v>
+        <v>-4.343773707278299</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.204335742235354</v>
+        <v>2.194760389637988</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.208132017490097</v>
+        <v>1.184193635996682</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.657505507357113</v>
+        <v>4.643142478461064</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.348142639658153</v>
+        <v>-4.372081021151569</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.380479041594339</v>
+        <v>2.370903688996973</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.208132017490097</v>
+        <v>1.184193635996682</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.844971732265407</v>
+        <v>4.830608703369357</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.514735864771676</v>
+        <v>-4.538674246265091</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.283244702903012</v>
+        <v>2.273669350305646</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.041538792376575</v>
+        <v>1.017600410883159</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.714418748551375</v>
+        <v>4.700055719655325</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.341671485389376</v>
+        <v>-4.365609866882791</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.35614685731765</v>
+        <v>2.346571504720284</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.041538792376575</v>
+        <v>1.017600410883159</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.718095151213093</v>
+        <v>4.703732122317043</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.312425504933679</v>
+        <v>-4.336363886427095</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.365463304623424</v>
+        <v>2.355887952026058</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.041538792376575</v>
+        <v>1.017600410883159</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.715713206336588</v>
+        <v>4.701350177440538</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.41935105281153</v>
+        <v>-4.443289434304946</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.319986324629919</v>
+        <v>2.310410972032552</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9346132444987235</v>
+        <v>0.9106748630053078</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.648851116767512</v>
+        <v>4.634488087871462</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.564369611318779</v>
+        <v>-4.588307992812195</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.263407703370254</v>
+        <v>2.253832350772887</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.789594685991475</v>
+        <v>0.7656563044980592</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.563268783806397</v>
+        <v>4.548905754910348</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.682711377103496</v>
+        <v>-4.706649758596912</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.31600223631412</v>
+        <v>2.306426883716753</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.8002807245543651</v>
+        <v>0.7763423430609493</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.669611646201885</v>
+        <v>4.655248617305835</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.734121799424204</v>
+        <v>-4.75806018091762</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.293223764511775</v>
+        <v>2.283648411914409</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.8002807245543651</v>
+        <v>0.7763423430609493</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.667397343327823</v>
+        <v>4.653034314431774</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.813541250631956</v>
+        <v>-4.837479632125372</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.261359112102964</v>
+        <v>2.251783759505598</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.8002807245543651</v>
+        <v>0.7763423430609493</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.667300471402113</v>
+        <v>4.652937442506063</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.909004248549174</v>
+        <v>-4.932942630042589</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.22316780649412</v>
+        <v>2.213592453896754</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.8002807245543651</v>
+        <v>0.7763423430609493</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.667294364960156</v>
+        <v>4.652931336064107</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.949024246592957</v>
+        <v>-4.972962628086373</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.205256203839217</v>
+        <v>2.195680851241851</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7602607265105812</v>
+        <v>0.7363223450171654</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.641378762696497</v>
+        <v>4.627015733800447</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.004393408725151</v>
+        <v>-5.028331790218567</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.188842356734066</v>
+        <v>2.1792670041367</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7602607265105812</v>
+        <v>0.7363223450171654</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.647112580444223</v>
+        <v>4.632749551548174</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.815468926386238</v>
+        <v>3.751790147746163</v>
       </c>
       <c r="C2064" t="n">
         <v>4.190494507880807</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.044067229324755</v>
+        <v>-5.073769570049394</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.172511191837158</v>
+        <v>2.160630255547302</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7205988338669589</v>
+        <v>0.6934773543390058</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.622853808200983</v>
+        <v>4.606580920484211</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240823.xlsx
+++ b/tame_output/ON/bt/strategyON_20240823.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-46.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-668.9%</t>
+          <t>-665.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-158.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-331.2%</t>
+          <t>-330.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-154.6%</t>
+          <t>-150.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>-27.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2064"/>
+  <dimension ref="A1:G2065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.351654121421943</v>
+        <v>-4.355272238160625</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.090228365581607</v>
+        <v>2.088781118886135</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9036248805047076</v>
+        <v>0.9000067637660256</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.373421366766957</v>
+        <v>4.371250496723747</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.358277368112301</v>
+        <v>-4.361895484850983</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.0894596970896</v>
+        <v>2.088012450394127</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8970016338143492</v>
+        <v>0.8933835170756672</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.371328048936878</v>
+        <v>4.369157178893668</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.255396778583708</v>
+        <v>-4.25901489532239</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.14346295877892</v>
+        <v>2.142015712083447</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9998822233429421</v>
+        <v>0.9962641066042601</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.445907428531916</v>
+        <v>4.443736558488706</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.278838817763795</v>
+        <v>-4.282456934502477</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.154288813280479</v>
+        <v>2.152841566585006</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9998822233429421</v>
+        <v>0.9962641066042601</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.46611009870551</v>
+        <v>4.463939228662301</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.296911326055406</v>
+        <v>-4.300529442794089</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.147059809963834</v>
+        <v>2.145612563268362</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9998822233429421</v>
+        <v>0.9962641066042601</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.46611009870551</v>
+        <v>4.463939228662301</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.528085119932038</v>
+        <v>-4.531703236670721</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.014842206006648</v>
+        <v>2.013394959311175</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9998822233429421</v>
+        <v>0.9962641066042601</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.426362012298976</v>
+        <v>4.424191142255768</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.496799099391583</v>
+        <v>-4.500417216130265</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.034379233219771</v>
+        <v>2.032931986524297</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.031168243883398</v>
+        <v>1.027550127144715</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.452156243620189</v>
+        <v>4.449985373576981</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.343773707278299</v>
+        <v>-4.347391824016981</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.194760389637988</v>
+        <v>2.193313142942515</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.184193635996682</v>
+        <v>1.180575519257999</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.643142478461064</v>
+        <v>4.640971608417855</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.372081021151569</v>
+        <v>-4.375699137890251</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.370903688996973</v>
+        <v>2.3694564423015</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.184193635996682</v>
+        <v>1.180575519257999</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.830608703369357</v>
+        <v>4.828437833326148</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.538674246265091</v>
+        <v>-4.542292363003773</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.273669350305646</v>
+        <v>2.272222103610173</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.017600410883159</v>
+        <v>1.013982294144477</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.700055719655325</v>
+        <v>4.697884849612116</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.365609866882791</v>
+        <v>-4.369227983621474</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.346571504720284</v>
+        <v>2.345124258024811</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.017600410883159</v>
+        <v>1.013982294144477</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.703732122317043</v>
+        <v>4.701561252273834</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.336363886427095</v>
+        <v>-4.339982003165777</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.355887952026058</v>
+        <v>2.354440705330584</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.017600410883159</v>
+        <v>1.013982294144477</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.701350177440538</v>
+        <v>4.699179307397329</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.443289434304946</v>
+        <v>-4.446907551043628</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.310410972032552</v>
+        <v>2.30896372533708</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9106748630053078</v>
+        <v>0.9070567462666256</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.634488087871462</v>
+        <v>4.632317217828254</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.588307992812195</v>
+        <v>-4.591926109550877</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.253832350772887</v>
+        <v>2.252385104077414</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7656563044980592</v>
+        <v>0.762038187759377</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.548905754910348</v>
+        <v>4.546734884867139</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.706649758596912</v>
+        <v>-4.710267875335594</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.306426883716753</v>
+        <v>2.30497963702128</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7763423430609493</v>
+        <v>0.7727242263222671</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.655248617305835</v>
+        <v>4.653077747262626</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.75806018091762</v>
+        <v>-4.761678297656302</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.283648411914409</v>
+        <v>2.282201165218936</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7763423430609493</v>
+        <v>0.7727242263222671</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.653034314431774</v>
+        <v>4.650863444388564</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.837479632125372</v>
+        <v>-4.841097748864054</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.251783759505598</v>
+        <v>2.250336512810124</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7763423430609493</v>
+        <v>0.7727242263222671</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.652937442506063</v>
+        <v>4.650766572462854</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.932942630042589</v>
+        <v>-4.936560746781272</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.213592453896754</v>
+        <v>2.212145207201281</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7763423430609493</v>
+        <v>0.7727242263222671</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.652931336064107</v>
+        <v>4.650760466020897</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.972962628086373</v>
+        <v>-4.976580744825055</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.195680851241851</v>
+        <v>2.194233604546378</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7363223450171654</v>
+        <v>0.7327042282784832</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.627015733800447</v>
+        <v>4.624844863757238</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.028331790218567</v>
+        <v>-5.031949906957249</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.1792670041367</v>
+        <v>2.177819757441227</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7363223450171654</v>
+        <v>0.7327042282784832</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.632749551548174</v>
+        <v>4.630578681504964</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,45 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.751790147746163</v>
+        <v>3.736843055396013</v>
       </c>
       <c r="C2064" t="n">
         <v>4.190494507880807</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.073769570049394</v>
+        <v>-5.037369813930686</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.160630255547302</v>
+        <v>2.175190157994785</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6934773543390058</v>
+        <v>0.7308750851325452</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.606580920484211</v>
+        <v>4.629019558960334</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" s="2" t="n">
+        <v>45527</v>
+      </c>
+      <c r="B2065" t="n">
+        <v>3.751779192735268</v>
+      </c>
+      <c r="C2065" t="n">
+        <v>4.189105234651398</v>
+      </c>
+      <c r="D2065" t="n">
+        <v>-5.037369813930686</v>
+      </c>
+      <c r="E2065" t="n">
+        <v>2.175190157994785</v>
+      </c>
+      <c r="F2065" t="n">
+        <v>0.7308750851325452</v>
+      </c>
+      <c r="G2065" t="n">
+        <v>4.182169031637765</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240823.xlsx
+++ b/tame_output/ON/bt/strategyON_20240823.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.1%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-665.3%</t>
+          <t>-668.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.7%</t>
+          <t>-160.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.8%</t>
+          <t>-331.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.9%</t>
+          <t>-154.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.355272238160625</v>
+        <v>-4.351654121421943</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.088781118886135</v>
+        <v>2.090228365581607</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9000067637660256</v>
+        <v>0.9036248805047076</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.371250496723747</v>
+        <v>4.373421366766957</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.361895484850983</v>
+        <v>-4.358277368112301</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.088012450394127</v>
+        <v>2.0894596970896</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8933835170756672</v>
+        <v>0.8970016338143492</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.369157178893668</v>
+        <v>4.371328048936878</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.25901489532239</v>
+        <v>-4.255396778583708</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.142015712083447</v>
+        <v>2.14346295877892</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9962641066042601</v>
+        <v>0.9998822233429421</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.443736558488706</v>
+        <v>4.445907428531916</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.282456934502477</v>
+        <v>-4.278838817763795</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.152841566585006</v>
+        <v>2.154288813280479</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9962641066042601</v>
+        <v>0.9998822233429421</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.463939228662301</v>
+        <v>4.46611009870551</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.300529442794089</v>
+        <v>-4.296911326055406</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.145612563268362</v>
+        <v>2.147059809963834</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9962641066042601</v>
+        <v>0.9998822233429421</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.463939228662301</v>
+        <v>4.46611009870551</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.531703236670721</v>
+        <v>-4.528085119932038</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.013394959311175</v>
+        <v>2.014842206006648</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9962641066042601</v>
+        <v>0.9998822233429421</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.424191142255768</v>
+        <v>4.426362012298976</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.500417216130265</v>
+        <v>-4.496799099391583</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.032931986524297</v>
+        <v>2.034379233219771</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.027550127144715</v>
+        <v>1.031168243883398</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.449985373576981</v>
+        <v>4.452156243620189</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.347391824016981</v>
+        <v>-4.343773707278299</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.193313142942515</v>
+        <v>2.194760389637988</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.180575519257999</v>
+        <v>1.184193635996682</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.640971608417855</v>
+        <v>4.643142478461064</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.375699137890251</v>
+        <v>-4.372081021151569</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.3694564423015</v>
+        <v>2.370903688996973</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.180575519257999</v>
+        <v>1.184193635996682</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.828437833326148</v>
+        <v>4.830608703369357</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.542292363003773</v>
+        <v>-4.538674246265091</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.272222103610173</v>
+        <v>2.273669350305646</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.013982294144477</v>
+        <v>1.017600410883159</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.697884849612116</v>
+        <v>4.700055719655325</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.369227983621474</v>
+        <v>-4.365609866882791</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.345124258024811</v>
+        <v>2.346571504720284</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.013982294144477</v>
+        <v>1.017600410883159</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.701561252273834</v>
+        <v>4.703732122317043</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.339982003165777</v>
+        <v>-4.336363886427095</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.354440705330584</v>
+        <v>2.355887952026058</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.013982294144477</v>
+        <v>1.017600410883159</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.699179307397329</v>
+        <v>4.701350177440538</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.446907551043628</v>
+        <v>-4.443289434304946</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.30896372533708</v>
+        <v>2.310410972032552</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9070567462666256</v>
+        <v>0.9106748630053078</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.632317217828254</v>
+        <v>4.634488087871462</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.591926109550877</v>
+        <v>-4.588307992812195</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.252385104077414</v>
+        <v>2.253832350772887</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.762038187759377</v>
+        <v>0.7656563044980592</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.546734884867139</v>
+        <v>4.548905754910348</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.710267875335594</v>
+        <v>-4.706649758596912</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.30497963702128</v>
+        <v>2.306426883716753</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7727242263222671</v>
+        <v>0.7763423430609493</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.653077747262626</v>
+        <v>4.655248617305835</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.761678297656302</v>
+        <v>-4.75806018091762</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.282201165218936</v>
+        <v>2.283648411914409</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7727242263222671</v>
+        <v>0.7763423430609493</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.650863444388564</v>
+        <v>4.653034314431774</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.841097748864054</v>
+        <v>-4.837479632125372</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.250336512810124</v>
+        <v>2.251783759505598</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7727242263222671</v>
+        <v>0.7763423430609493</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.650766572462854</v>
+        <v>4.652937442506063</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.936560746781272</v>
+        <v>-4.932942630042589</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.212145207201281</v>
+        <v>2.213592453896754</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7727242263222671</v>
+        <v>0.7763423430609493</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.650760466020897</v>
+        <v>4.652931336064107</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.976580744825055</v>
+        <v>-4.972962628086373</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.194233604546378</v>
+        <v>2.195680851241851</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7327042282784832</v>
+        <v>0.7363223450171654</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.624844863757238</v>
+        <v>4.627015733800447</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.031949906957249</v>
+        <v>-5.028331790218567</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.177819757441227</v>
+        <v>2.1792670041367</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7327042282784832</v>
+        <v>0.7363223450171654</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.630578681504964</v>
+        <v>4.632749551548174</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.190494507880807</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.037369813930686</v>
+        <v>-5.073769570049394</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.175190157994785</v>
+        <v>2.160630255547302</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7308750851325452</v>
+        <v>0.6934773543390058</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.629019558960334</v>
+        <v>4.606580920484211</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,13 +49046,13 @@
         <v>4.189105234651398</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.037369813930686</v>
+        <v>-5.073769570049394</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.175190157994785</v>
+        <v>2.160630255547302</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7308750851325452</v>
+        <v>0.6934773543390058</v>
       </c>
       <c r="G2065" t="n">
         <v>4.182169031637765</v>

--- a/tame_output/ON/bt/strategyON_20240823.xlsx
+++ b/tame_output/ON/bt/strategyON_20240823.xlsx
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.751779192735268</v>
+        <v>3.751779192735269</v>
       </c>
       <c r="C2065" t="n">
         <v>4.189105234651398</v>

--- a/tame_output/ON/bt/strategyON_20240823.xlsx
+++ b/tame_output/ON/bt/strategyON_20240823.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>109.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-44.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-48.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-668.9%</t>
+          <t>-662.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-155.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>16.6%</t>
         </is>
       </c>
     </row>
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.751779192735269</v>
+        <v>3.751779192735268</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.189105234651398</v>
+        <v>4.210368900731126</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.073769570049394</v>
+        <v>-5.005788108371808</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.160630255547302</v>
+        <v>2.207697233068656</v>
       </c>
       <c r="F2065" t="n">
         <v>0.6934773543390058</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.182169031637765</v>
+        <v>4.62645531333453</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240823.xlsx
+++ b/tame_output/ON/bt/strategyON_20240823.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.2%</t>
+          <t>-662.1%</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-155.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-331.2%</t>
+          <t>-331.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-154.6%</t>
+          <t>-155.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.351654121421943</v>
+        <v>-4.327715739928527</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.090228365581607</v>
+        <v>2.099803718178974</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9036248805047076</v>
+        <v>0.9275632619981236</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.373421366766957</v>
+        <v>4.387784395663006</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.358277368112301</v>
+        <v>-4.368870859496748</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.0894596970896</v>
+        <v>2.085222300535821</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8970016338143492</v>
+        <v>0.8864081424299026</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.371328048936878</v>
+        <v>4.36497195410621</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.255396778583708</v>
+        <v>-4.265990269968155</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.14346295877892</v>
+        <v>2.139225562225141</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9998822233429421</v>
+        <v>0.9892887319584955</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.445907428531916</v>
+        <v>4.439551333701248</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.278838817763795</v>
+        <v>-4.289432309148242</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.154288813280479</v>
+        <v>2.150051416726701</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9998822233429421</v>
+        <v>0.9892887319584955</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.46611009870551</v>
+        <v>4.459754003874842</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.296911326055406</v>
+        <v>-4.307504817439853</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.147059809963834</v>
+        <v>2.142822413410056</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9998822233429421</v>
+        <v>0.9892887319584955</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.46611009870551</v>
+        <v>4.459754003874842</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.528085119932038</v>
+        <v>-4.538678611316485</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.014842206006648</v>
+        <v>2.010604809452869</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9998822233429421</v>
+        <v>0.9892887319584955</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.426362012298976</v>
+        <v>4.420005917468308</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.496799099391583</v>
+        <v>-4.50739259077603</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.034379233219771</v>
+        <v>2.030141836665992</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.031168243883398</v>
+        <v>1.020574752498951</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.452156243620189</v>
+        <v>4.445800148789522</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.343773707278299</v>
+        <v>-4.354367198662746</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.194760389637988</v>
+        <v>2.190522993084209</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.184193635996682</v>
+        <v>1.173600144612235</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.643142478461064</v>
+        <v>4.636786383630397</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.372081021151569</v>
+        <v>-4.382674512536016</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.370903688996973</v>
+        <v>2.366666292443194</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.184193635996682</v>
+        <v>1.173600144612235</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.830608703369357</v>
+        <v>4.824252608538689</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.538674246265091</v>
+        <v>-4.549267737649538</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.273669350305646</v>
+        <v>2.269431953751867</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.017600410883159</v>
+        <v>1.007006919498713</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.700055719655325</v>
+        <v>4.693699624824657</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.365609866882791</v>
+        <v>-4.376203358267238</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.346571504720284</v>
+        <v>2.342334108166505</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.017600410883159</v>
+        <v>1.007006919498713</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.703732122317043</v>
+        <v>4.697376027486375</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.336363886427095</v>
+        <v>-4.346957377811542</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.355887952026058</v>
+        <v>2.351650555472279</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.017600410883159</v>
+        <v>1.007006919498713</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.701350177440538</v>
+        <v>4.69499408260987</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.443289434304946</v>
+        <v>-4.453882925689393</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.310410972032552</v>
+        <v>2.306173575478773</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9106748630053078</v>
+        <v>0.9000813716208612</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.634488087871462</v>
+        <v>4.628131993040795</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.588307992812195</v>
+        <v>-4.598901484196642</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.253832350772887</v>
+        <v>2.249594954219108</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7656563044980592</v>
+        <v>0.7550628131136127</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.548905754910348</v>
+        <v>4.54254966007968</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.706649758596912</v>
+        <v>-4.717243249981359</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.306426883716753</v>
+        <v>2.302189487162974</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7763423430609493</v>
+        <v>0.7657488516765028</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.655248617305835</v>
+        <v>4.648892522475167</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.75806018091762</v>
+        <v>-4.768653672302067</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.283648411914409</v>
+        <v>2.27941101536063</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7763423430609493</v>
+        <v>0.7657488516765028</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.653034314431774</v>
+        <v>4.646678219601106</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.837479632125372</v>
+        <v>-4.848073123509819</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.251783759505598</v>
+        <v>2.247546362951819</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7763423430609493</v>
+        <v>0.7657488516765028</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.652937442506063</v>
+        <v>4.646581347675395</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.932942630042589</v>
+        <v>-4.943536121427036</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.213592453896754</v>
+        <v>2.209355057342975</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7763423430609493</v>
+        <v>0.7657488516765028</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.652931336064107</v>
+        <v>4.646575241233439</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.972962628086373</v>
+        <v>-4.98355611947082</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.195680851241851</v>
+        <v>2.191443454688072</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7363223450171654</v>
+        <v>0.7257288536327189</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.627015733800447</v>
+        <v>4.620659638969779</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.028331790218567</v>
+        <v>-5.038925281603014</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.1792670041367</v>
+        <v>2.175029607582921</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7363223450171654</v>
+        <v>0.7257288536327189</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.632749551548174</v>
+        <v>4.626393456717506</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.190494507880807</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.073769570049394</v>
+        <v>-5.084363061433841</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.160630255547302</v>
+        <v>2.156392858993523</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6934773543390058</v>
+        <v>0.6828838629545593</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.606580920484211</v>
+        <v>4.600224825653543</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.751779192735268</v>
+        <v>3.738570638853659</v>
       </c>
       <c r="C2065" t="n">
         <v>4.210368900731126</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.005788108371808</v>
+        <v>-5.005347520260901</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.207697233068656</v>
+        <v>2.207873468313019</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6934773543390058</v>
+        <v>0.6828838629545593</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.62645531333453</v>
+        <v>4.620099218503862</v>
       </c>
     </row>
   </sheetData>
